--- a/artfynd/A 10107-2023 artfynd.xlsx
+++ b/artfynd/A 10107-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10107-2023 artfynd.xlsx
+++ b/artfynd/A 10107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99961576</v>
+        <v>116505746</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogstorp 700m nno, Srm</t>
+          <t>Skogstorp 800m NO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607459.59557795</v>
+        <v>607462</v>
       </c>
       <c r="R2" t="n">
-        <v>6551720.165871071</v>
+        <v>6551782</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,6 +765,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,53 +787,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116501766</v>
+        <v>99961576</v>
       </c>
       <c r="B3" t="n">
-        <v>96728</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogstorp 750mNO, Srm</t>
+          <t>Skogstorp 700m nno, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607227</v>
+        <v>607460</v>
       </c>
       <c r="R3" t="n">
-        <v>6551789</v>
+        <v>6551720</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,37 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116505746</v>
+        <v>99961511</v>
       </c>
       <c r="B4" t="n">
-        <v>102801</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>706</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,17 +936,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogstorp 800m NO, Srm</t>
+          <t>Skogstorp 800m nnv, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607462</v>
+        <v>607485</v>
       </c>
       <c r="R4" t="n">
-        <v>6551782</v>
+        <v>6551789</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,11 +993,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hygge</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1026,6 +1005,109 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116501766</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogstorp 750mNO, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607227</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6551789</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10107-2023 artfynd.xlsx
+++ b/artfynd/A 10107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116505746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99961576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99961511</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,8 +1128,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116501766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>